--- a/02_DIA_inicio_2026_analisis_assets/resumen_general_nt.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/resumen_general_nt.xlsx
@@ -661,13 +661,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D6FDCD7-40DD-40DC-8127-EC97EC304D66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD8C3872-A1A4-4C82-A077-4E268478E1FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AAB69B-7AAB-44D3-95EB-D2AAF24E681F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C571AA78-AA38-4C58-AD45-DF669239DB6C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CFD5944-010C-4389-9706-C4CD31746898}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84DD08F1-6873-4D17-AE1B-7B3278CADDAF}"/>
 </file>